--- a/relatorio_vendas_margens_2026-06-16_2026-07-16.xlsx
+++ b/relatorio_vendas_margens_2026-06-16_2026-07-16.xlsx
@@ -441,7 +441,7 @@
         <v>16/07/2026</v>
       </c>
       <c r="B2" t="str">
-        <v>02:27</v>
+        <v>02:32</v>
       </c>
       <c r="C2" t="str">
         <v>Test Store</v>

--- a/relatorio_vendas_margens_2026-06-16_2026-07-16.xlsx
+++ b/relatorio_vendas_margens_2026-06-16_2026-07-16.xlsx
@@ -441,7 +441,7 @@
         <v>16/07/2026</v>
       </c>
       <c r="B2" t="str">
-        <v>02:32</v>
+        <v>02:33</v>
       </c>
       <c r="C2" t="str">
         <v>Test Store</v>

--- a/relatorio_vendas_margens_2026-06-16_2026-07-16.xlsx
+++ b/relatorio_vendas_margens_2026-06-16_2026-07-16.xlsx
@@ -441,7 +441,7 @@
         <v>16/07/2026</v>
       </c>
       <c r="B2" t="str">
-        <v>02:33</v>
+        <v>02:34</v>
       </c>
       <c r="C2" t="str">
         <v>Test Store</v>

--- a/relatorio_vendas_margens_2026-06-16_2026-07-16.xlsx
+++ b/relatorio_vendas_margens_2026-06-16_2026-07-16.xlsx
@@ -441,7 +441,7 @@
         <v>16/07/2026</v>
       </c>
       <c r="B2" t="str">
-        <v>02:34</v>
+        <v>02:42</v>
       </c>
       <c r="C2" t="str">
         <v>Test Store</v>

--- a/relatorio_vendas_margens_2026-06-16_2026-07-16.xlsx
+++ b/relatorio_vendas_margens_2026-06-16_2026-07-16.xlsx
@@ -441,7 +441,7 @@
         <v>16/07/2026</v>
       </c>
       <c r="B2" t="str">
-        <v>02:42</v>
+        <v>02:43</v>
       </c>
       <c r="C2" t="str">
         <v>Test Store</v>
